--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.0314872603191</v>
+        <v>4.880116679801853</v>
       </c>
       <c r="D2" t="n">
-        <v>29.83353513359742</v>
+        <v>4.84794945920958</v>
       </c>
       <c r="E2" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F2" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.79296557973012</v>
+        <v>3.378856906706145</v>
       </c>
       <c r="D3" t="n">
-        <v>20.67304463766576</v>
+        <v>3.359369753620686</v>
       </c>
       <c r="E3" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F3" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.02513861901156</v>
+        <v>8.291585025589379</v>
       </c>
       <c r="D4" t="n">
-        <v>41.91072216255516</v>
+        <v>6.810492351415213</v>
       </c>
       <c r="E4" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F4" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.66209651365796</v>
+        <v>7.095090683469418</v>
       </c>
       <c r="D5" t="n">
-        <v>46.42302699823666</v>
+        <v>7.543741887213457</v>
       </c>
       <c r="E5" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.55931257611714</v>
+        <v>5.453388293619035</v>
       </c>
       <c r="D6" t="n">
-        <v>36.65773618532265</v>
+        <v>5.956882130114932</v>
       </c>
       <c r="E6" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F6" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.75743704324224</v>
+        <v>3.373083519526864</v>
       </c>
       <c r="D7" t="n">
-        <v>20.78866339770503</v>
+        <v>3.378157802127068</v>
       </c>
       <c r="E7" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F7" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.08831359800476</v>
+        <v>6.351850959675773</v>
       </c>
       <c r="D8" t="n">
-        <v>17.76013623400507</v>
+        <v>2.886022138025825</v>
       </c>
       <c r="E8" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F8" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.27972089038715</v>
+        <v>5.082954644687911</v>
       </c>
       <c r="D9" t="n">
-        <v>31.40885484950626</v>
+        <v>5.103938913044767</v>
       </c>
       <c r="E9" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F9" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.01233212281259</v>
+        <v>5.364503969957045</v>
       </c>
       <c r="D10" t="n">
-        <v>33.23099956599187</v>
+        <v>5.400037429473678</v>
       </c>
       <c r="E10" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F10" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.81735718614452</v>
+        <v>6.795320542748485</v>
       </c>
       <c r="D11" t="n">
-        <v>42.07470525524867</v>
+        <v>6.83713960397791</v>
       </c>
       <c r="E11" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F11" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.2964110994578</v>
+        <v>1.998166803661893</v>
       </c>
       <c r="D12" t="n">
-        <v>14.86665002049369</v>
+        <v>2.415830628330225</v>
       </c>
       <c r="E12" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F12" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.83964730123004</v>
+        <v>6.473942686449883</v>
       </c>
       <c r="D13" t="n">
-        <v>12.51024293676042</v>
+        <v>2.032914477223568</v>
       </c>
       <c r="E13" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F13" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>46.61326779477088</v>
+        <v>7.574656016650269</v>
       </c>
       <c r="D14" t="n">
-        <v>39.09389550517044</v>
+        <v>6.352758019590196</v>
       </c>
       <c r="E14" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F14" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.45658124058571</v>
+        <v>6.411694451595179</v>
       </c>
       <c r="D15" t="n">
-        <v>31.77449292254983</v>
+        <v>5.163355099914348</v>
       </c>
       <c r="E15" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F15" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>12.19319037458691</v>
+        <v>1.981393435870373</v>
       </c>
       <c r="D16" t="n">
-        <v>17.54726278359413</v>
+        <v>2.851430202334047</v>
       </c>
       <c r="E16" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F16" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.66035602492039</v>
+        <v>4.169807854049564</v>
       </c>
       <c r="D17" t="n">
-        <v>26.67324063458613</v>
+        <v>4.334401603120246</v>
       </c>
       <c r="E17" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F17" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>37.98312831254462</v>
+        <v>6.172258350788502</v>
       </c>
       <c r="D18" t="n">
-        <v>34.90253102466675</v>
+        <v>5.671661291508348</v>
       </c>
       <c r="E18" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F18" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.35260869713563</v>
+        <v>6.23229891328454</v>
       </c>
       <c r="D19" t="n">
-        <v>37.67777561927666</v>
+        <v>6.122638538132457</v>
       </c>
       <c r="E19" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F19" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>54.37487120935984</v>
+        <v>8.835916571520974</v>
       </c>
       <c r="D20" t="n">
-        <v>47.65262415233415</v>
+        <v>7.743551424754299</v>
       </c>
       <c r="E20" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F20" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>46.54438395255819</v>
+        <v>7.563462392290706</v>
       </c>
       <c r="D21" t="n">
-        <v>40.88147821047314</v>
+        <v>6.643240209201886</v>
       </c>
       <c r="E21" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F21" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>73.10512790662251</v>
+        <v>11.87958328482616</v>
       </c>
       <c r="D22" t="n">
-        <v>62.06343142854113</v>
+        <v>10.08530760713793</v>
       </c>
       <c r="E22" t="n">
-        <v>13.90923142833811</v>
+        <v>2.260250107104944</v>
       </c>
       <c r="F22" t="n">
-        <v>12.1738883669134</v>
+        <v>1.978256859623428</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
